--- a/astro-site/public/dl/plan-negocio-paellero-eventos/calculadora-pricing-eventos-paellero.xlsx
+++ b/astro-site/public/dl/plan-negocio-paellero-eventos/calculadora-pricing-eventos-paellero.xlsx
@@ -560,7 +560,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -715,7 +714,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
@@ -851,7 +849,6 @@
         </is>
       </c>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
@@ -910,7 +907,7 @@
         </is>
       </c>
       <c r="B30" s="11">
-        <f>B29/B6</f>
+        <f>IFERROR(B29/B6,"")</f>
         <v>20.69125</v>
       </c>
     </row>
@@ -920,7 +917,7 @@
           <t>Anticipo 30 % a cobrar al firmar</t>
         </is>
       </c>
-      <c r="B31" s="13">
+      <c r="B31" s="11">
         <f>B29*0.3</f>
         <v>496.59</v>
       </c>
@@ -948,29 +945,49 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="A4:D4"/>
     <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="C11:E11"/>
     <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C16:E16"/>
     <mergeCell ref="C8:E8"/>
-    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="C19:E19"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="C21:E21"/>
     <mergeCell ref="C13:E13"/>
     <mergeCell ref="C18:E18"/>
     <mergeCell ref="A25:D25"/>
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="C10:E10"/>
   </mergeCells>
+  <dataValidations count="6">
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Tipo de cliente" error="Elige B2C o B2B de la lista." type="list" errorStyle="stop">
+      <formula1>"B2C,B2B"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Tipo de paella" error="Elige un tipo de paella de la lista (con su tilde): el recargo se calcula a partir de él." type="list" errorStyle="stop">
+      <formula1>"Valenciana,Marisco,Senyoret,Negro,Paella mixta,Banda,Fideuá,Montaña"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Concepto premium" error="Elige «sí» o «no» de la lista (con tilde)." type="list" errorStyle="stop">
+      <formula1>"sí,no"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B11" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Show cooking" error="Elige «sí» o «no» de la lista (con tilde)." type="list" errorStyle="stop">
+      <formula1>"sí,no"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B12" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Suministra cliente" error="Elige «sí» o «no» de la lista (con tilde)." type="list" errorStyle="stop">
+      <formula1>"sí,no"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B13" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Estación" error="Elige «seca» o «lluvia» de la lista." type="list" errorStyle="stop">
+      <formula1>"seca,lluvia"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -1017,7 +1034,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="14" t="inlineStr">
         <is>
@@ -1382,8 +1398,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A1:J1"/>
   </mergeCells>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>

--- a/astro-site/public/dl/plan-negocio-paellero-eventos/calculadora-pricing-eventos-paellero.xlsx
+++ b/astro-site/public/dl/plan-negocio-paellero-eventos/calculadora-pricing-eventos-paellero.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Particular o Empresa: cambia los tramos de cancelación (contratos del kit). Ayuntamientos y comisiones de fiestas cuentan como Empresa.</t>
+          <t>Particular o Empresa: cambia los tramos de cancelación (contratos del kit). Las comisiones de fiestas y peñas cuentan como Empresa. Un ayuntamiento no adelanta el 30 %: compra por contrato menor y paga a 30 días desde la conformidad (art. 198.4 de la Ley 9/2017); pon 0 % de anticipo.</t>
         </is>
       </c>
     </row>
@@ -636,11 +636,11 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>8.9</v>
+        <v>6.7</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Tu escandallo. La carta del kit da el food cost por ración con acompañamientos (7,60-16,50 €) para bodas y empresas; una paella sola de fiesta popular ronda 2,00-2,50 €.</t>
+          <t>Tu escandallo. La carta del kit da el food cost de la paella sola (2,00-6,00 € por ración): suma los entrantes, el pan y el alioli si los sirves. Una paella sola de fiesta popular ronda 2,00-2,50 €.</t>
         </is>
       </c>
     </row>
@@ -651,11 +651,11 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>0.4</v>
+        <v>0.48</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Estimación del kit: 0,30-0,45 €. Pon 0 si el cliente pone el menaje.</t>
+          <t>Estimación del kit: 0,30-0,50 €. Pon 0 si el cliente pone el menaje.</t>
         </is>
       </c>
     </row>
@@ -915,7 +915,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Tres paelleras son el techo de un paellero (manual técnico 1.2).</t>
+          <t>Regla conservadora: un paellero lleva hasta tres paelleras; con ayudante, cuatro (manual técnico del kit, tabla para 100 invitados).</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
       </c>
       <c r="B32" s="12">
         <f>$B$9*$B$6</f>
-        <v>1068.0</v>
+        <v>804.0</v>
       </c>
     </row>
     <row r="33">
@@ -981,7 +981,7 @@
       </c>
       <c r="B33" s="12">
         <f>$B$10*$B$6</f>
-        <v>48.0</v>
+        <v>57.599999999999994</v>
       </c>
     </row>
     <row r="34">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="B37" s="12">
         <f>$B$32+$B$33+$B$34+$B$35+$B$36</f>
-        <v>1988.6799999999998</v>
+        <v>1734.2800000000002</v>
       </c>
     </row>
     <row r="38">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="B38" s="12">
         <f>$B$37/$B$6</f>
-        <v>16.572333333333333</v>
+        <v>14.452333333333335</v>
       </c>
     </row>
     <row r="39">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="B39" s="14">
         <f>ROUNDUP($B$37/(1-$B$21)/$B$6*(1+$B$20)*2,0)/2</f>
-        <v>28.0</v>
+        <v>24.5</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="B40" s="14">
         <f>$B$39*(1+$B$22)</f>
-        <v>30.800000000000004</v>
+        <v>26.950000000000003</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="B41" s="12">
         <f>$B$39*$B$6</f>
-        <v>3360.0</v>
+        <v>2940.0</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B43" s="12">
         <f>$B$41+$B$42</f>
-        <v>3426.5</v>
+        <v>3006.5</v>
       </c>
     </row>
     <row r="44">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="B44" s="12">
         <f>$B$43*$B$22</f>
-        <v>342.65000000000003</v>
+        <v>300.65000000000003</v>
       </c>
     </row>
     <row r="45">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="B45" s="14">
         <f>$B$43+$B$44</f>
-        <v>3769.15</v>
+        <v>3307.15</v>
       </c>
     </row>
     <row r="46">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="B46" s="12">
         <f>$B$45*$B$23</f>
-        <v>1130.745</v>
+        <v>992.145</v>
       </c>
     </row>
     <row r="47">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="B47" s="12">
         <f>$B$45-$B$46</f>
-        <v>2638.405</v>
+        <v>2315.005</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B48" s="12">
         <f>$B$41-$B$37</f>
-        <v>1371.3200000000002</v>
+        <v>1205.7199999999998</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B49" s="15">
         <f>IF($B$41=0,0,$B$48/$B$41)</f>
-        <v>0.4081309523809524</v>
+        <v>0.4101088435374149</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="B50" s="12">
         <f>IF($B$5="Particular",$B$45*0.3,0)</f>
-        <v>1130.745</v>
+        <v>992.145</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="B51" s="12">
         <f>IF($B$5="Particular",$B$45*0.5,$B$46*0.3)</f>
-        <v>1884.575</v>
+        <v>1653.575</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
@@ -1239,12 +1239,12 @@
         </is>
       </c>
       <c r="B52" s="12">
-        <f>IF($B$5="Particular",$B$45*0.75,$B$46*0.6+200)</f>
-        <v>2826.8625</v>
+        <f>IF($B$5="Particular",$B$45*0.75,IF($B$46=0,0,$B$46*0.6+200))</f>
+        <v>2480.3625</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Particular: el 75 % del total. Empresa: el 60 % del anticipo más 200 € de gestión.</t>
+          <t>Particular: el 75 % del total. Empresa: el 60 % del anticipo más 200 € de gestión (0 si no hay anticipo).</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="B53" s="12">
         <f>$B$45</f>
-        <v>3769.15</v>
+        <v>3307.15</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>TABLA DE ESCALADO POR PAELLERA (manual técnico 1.2, tabla 1): diámetro en cm</t>
+          <t>TABLA DE ESCALADO POR PAELLERA (manual técnico del kit, tabla 1): diámetro en cm</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>8.9</v>
+        <v>6.7</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>8.5</v>
+        <v>5.7</v>
       </c>
       <c r="D9" s="12" t="n">
         <v>2.25</v>
@@ -1605,7 +1605,7 @@
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>0.4</v>
+        <v>0.48</v>
       </c>
       <c r="C10" s="12" t="n">
         <v>0.45</v>
@@ -1781,10 +1781,10 @@
         </is>
       </c>
       <c r="B21" s="20" t="n">
-        <v>0.4</v>
+        <v>0.48</v>
       </c>
       <c r="C21" s="20" t="n">
-        <v>0.45</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="D21" s="20" t="n">
         <v>0.12</v>
@@ -1819,7 +1819,7 @@
         <v>0.3</v>
       </c>
       <c r="D23" s="20" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" ht="32" customHeight="1">
@@ -1966,11 +1966,11 @@
       </c>
       <c r="B32" s="12">
         <f>$B$9*$B$6</f>
-        <v>1068.0</v>
+        <v>804.0</v>
       </c>
       <c r="C32" s="12">
         <f>$C$9*$C$6</f>
-        <v>595.0</v>
+        <v>399.0</v>
       </c>
       <c r="D32" s="12">
         <f>$D$9*$D$6</f>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="B33" s="12">
         <f>$B$10*$B$6</f>
-        <v>48.0</v>
+        <v>57.599999999999994</v>
       </c>
       <c r="C33" s="12">
         <f>$C$10*$C$6</f>
@@ -2061,11 +2061,11 @@
       </c>
       <c r="B37" s="12">
         <f>$B$32+$B$33+$B$34+$B$35+$B$36</f>
-        <v>1988.6799999999998</v>
+        <v>1734.2800000000002</v>
       </c>
       <c r="C37" s="12">
         <f>$C$32+$C$33+$C$34+$C$35+$C$36</f>
-        <v>877.335</v>
+        <v>681.335</v>
       </c>
       <c r="D37" s="12">
         <f>$D$32+$D$33+$D$34+$D$35+$D$36</f>
@@ -2080,11 +2080,11 @@
       </c>
       <c r="B38" s="12">
         <f>$B$37/$B$6</f>
-        <v>16.572333333333333</v>
+        <v>14.452333333333335</v>
       </c>
       <c r="C38" s="12">
         <f>$C$37/$C$6</f>
-        <v>12.533357142857144</v>
+        <v>9.733357142857143</v>
       </c>
       <c r="D38" s="12">
         <f>$D$37/$D$6</f>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="C39" s="14">
         <f>ROUNDUP($C$37/(1-$C$21)/$C$6*(1+$C$20)*2,0)/2</f>
-        <v>25.0</v>
+        <v>24.0</v>
       </c>
       <c r="D39" s="14">
         <f>ROUNDUP($D$37/(1-$D$21)/$D$6*(1+$D$20)*2,0)/2</f>
@@ -2122,7 +2122,7 @@
       </c>
       <c r="C40" s="14">
         <f>$C$39*(1+$C$22)</f>
-        <v>27.500000000000004</v>
+        <v>26.400000000000002</v>
       </c>
       <c r="D40" s="14">
         <f>$D$39*(1+$D$22)</f>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="C41" s="12">
         <f>$C$39*$C$6</f>
-        <v>1750.0</v>
+        <v>1680.0</v>
       </c>
       <c r="D41" s="12">
         <f>$D$39*$D$6</f>
@@ -2179,7 +2179,7 @@
       </c>
       <c r="C43" s="12">
         <f>$C$41+$C$42</f>
-        <v>1797.5</v>
+        <v>1727.5</v>
       </c>
       <c r="D43" s="12">
         <f>$D$41+$D$42</f>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="C44" s="12">
         <f>$C$43*$C$22</f>
-        <v>179.75</v>
+        <v>172.75</v>
       </c>
       <c r="D44" s="12">
         <f>$D$43*$D$22</f>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="C45" s="14">
         <f>$C$43+$C$44</f>
-        <v>1977.25</v>
+        <v>1900.25</v>
       </c>
       <c r="D45" s="14">
         <f>$D$43+$D$44</f>
@@ -2236,11 +2236,11 @@
       </c>
       <c r="C46" s="12">
         <f>$C$45*$C$23</f>
-        <v>593.175</v>
+        <v>570.0749999999999</v>
       </c>
       <c r="D46" s="12">
         <f>$D$45*$D$23</f>
-        <v>612.81</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="47">
@@ -2255,11 +2255,11 @@
       </c>
       <c r="C47" s="12">
         <f>$C$45-$C$46</f>
-        <v>1384.075</v>
+        <v>1330.1750000000002</v>
       </c>
       <c r="D47" s="12">
         <f>$D$45-$D$46</f>
-        <v>1429.89</v>
+        <v>2042.7</v>
       </c>
     </row>
     <row r="48">
@@ -2270,11 +2270,11 @@
       </c>
       <c r="B48" s="12">
         <f>$B$41-$B$37</f>
-        <v>1371.3200000000002</v>
+        <v>1625.7199999999998</v>
       </c>
       <c r="C48" s="12">
         <f>$C$41-$C$37</f>
-        <v>872.665</v>
+        <v>998.665</v>
       </c>
       <c r="D48" s="12">
         <f>$D$41-$D$37</f>
@@ -2289,11 +2289,11 @@
       </c>
       <c r="B49" s="15">
         <f>IF($B$41=0,0,$B$48/$B$41)</f>
-        <v>0.4081309523809524</v>
+        <v>0.48384523809523805</v>
       </c>
       <c r="C49" s="15">
         <f>IF($C$41=0,0,$C$48/$C$41)</f>
-        <v>0.49866571428571427</v>
+        <v>0.5944434523809523</v>
       </c>
       <c r="D49" s="15">
         <f>IF($D$41=0,0,$D$48/$D$41)</f>
@@ -2331,11 +2331,11 @@
       </c>
       <c r="C51" s="12">
         <f>IF($C$5="Particular",$C$45*0.5,$C$46*0.3)</f>
-        <v>177.9525</v>
+        <v>171.02249999999998</v>
       </c>
       <c r="D51" s="12">
         <f>IF($D$5="Particular",$D$45*0.5,$D$46*0.3)</f>
-        <v>183.843</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="52">
@@ -2345,16 +2345,16 @@
         </is>
       </c>
       <c r="B52" s="12">
-        <f>IF($B$5="Particular",$B$45*0.75,$B$46*0.6+200)</f>
+        <f>IF($B$5="Particular",$B$45*0.75,IF($B$46=0,0,$B$46*0.6+200))</f>
         <v>2826.8625</v>
       </c>
       <c r="C52" s="12">
-        <f>IF($C$5="Particular",$C$45*0.75,$C$46*0.6+200)</f>
-        <v>555.905</v>
+        <f>IF($C$5="Particular",$C$45*0.75,IF($C$46=0,0,$C$46*0.6+200))</f>
+        <v>542.045</v>
       </c>
       <c r="D52" s="12">
-        <f>IF($D$5="Particular",$D$45*0.75,$D$46*0.6+200)</f>
-        <v>567.6859999999999</v>
+        <f>IF($D$5="Particular",$D$45*0.75,IF($D$46=0,0,$D$46*0.6+200))</f>
+        <v>0.0</v>
       </c>
     </row>
     <row r="53">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="C53" s="12">
         <f>$C$45</f>
-        <v>1977.25</v>
+        <v>1900.25</v>
       </c>
       <c r="D53" s="12">
         <f>$D$45</f>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Particular, 120 invitados, dos variedades en paellera de 120 cm más entrantes (la materia prima incluye los acompañamientos), carpa y mesas alquiladas repercutidas y precio con IVA.</t>
+          <t>Particular, 120 invitados, dos variedades en paellera de 120 cm más entrantes (la materia prima incluye la paella y los entrantes), carpa y mesas alquiladas repercutidas, margen objetivo del 48 % y precio con IVA.</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Empresa: presupuesto «+ IVA», cocina a la vista con el 8 % de suplemento y tramos de cancelación sobre el anticipo.</t>
+          <t>Empresa: presupuesto «+ IVA», cocina a la vista con el 8 % de suplemento, margen alto por el show cooking y el servicio a empresa, y tramos de cancelación sobre el anticipo.</t>
         </is>
       </c>
     </row>
@@ -2415,7 +2415,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Ayuntamiento = Empresa. 400 raciones en paelleras de 150 cm, menaje desechable y margen bajo por volumen: el precio por ración queda en el orden de 4-5 € (en 2025, Sayalonga cobró 1.480 € por 400 raciones).</t>
+          <t>400 raciones en paelleras de 150 cm, menaje desechable y margen bajo por volumen: el precio por ración queda en el orden de 4-5 € (en 2025, Sayalonga cobró 1.480 € por 400 raciones). Sin anticipo: el ayuntamiento paga a 30 días desde la conformidad; los tramos de cancelación de los contratos del kit no se le aplican (contrata con su propio pliego o contrato menor). El kit trae una paellera de 150 cm: alquila las demás o usa varias de 120 cm.</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>1. Elige el cliente (Particular o Empresa; ayuntamientos y comisiones de fiestas cuentan como Empresa), los invitados y el diámetro de paellera.</t>
+          <t>1. Elige el cliente (Particular o Empresa; las comisiones de fiestas y peñas cuentan como Empresa; a un ayuntamiento, que paga a 30 días desde la conformidad, ponle 0 % de anticipo), los invitados y el diámetro de paellera.</t>
         </is>
       </c>
     </row>
@@ -2537,10 +2537,10 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="16" customHeight="1">
+    <row r="14" ht="30" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Los pagos en efectivo con particulares sólo valen hasta 1.000 € (art. 7 de la Ley 7/2012).</t>
+          <t>Los pagos en efectivo con particulares solo valen por debajo de 1.000 €: la ley prohíbe pagar en efectivo 1.000 € o más (art. 7 de la Ley 7/2012).</t>
         </is>
       </c>
     </row>

--- a/astro-site/public/dl/plan-negocio-paellero-eventos/calculadora-pricing-eventos-paellero.xlsx
+++ b/astro-site/public/dl/plan-negocio-paellero-eventos/calculadora-pricing-eventos-paellero.xlsx
@@ -2403,7 +2403,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Empresa: presupuesto «+ IVA», cocina a la vista con el 8 % de suplemento, margen alto por el show cooking y el servicio a empresa, y tramos de cancelación sobre el anticipo.</t>
+          <t>Empresa: presupuesto «+ IVA», cocina a la vista con el 8 % de suplemento, margen alto por el show cooking y el servicio a empresa (el margen objetivo cambia por canal: 48 % en la boda, 56 % aquí), y tramos de cancelación sobre el anticipo.</t>
         </is>
       </c>
     </row>
